--- a/datasets/2025_2T/estadisticas_FP_P04.xlsx
+++ b/datasets/2025_2T/estadisticas_FP_P04.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,280 +434,298 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>SIT_1, 2 o 3</t>
+          <t>SIT</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>PARCIAL_100</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>EXAMEN 1E_100</t>
+          <t>EXAMEN 1E</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>TEMA 1E-1_25</t>
+          <t>TEMA 1E-1</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>TEMA 1E-2_25</t>
+          <t>TEMA 1E-2</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>TEMA 1E-3_25</t>
+          <t>TEMA 1E-3</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>TEMA 1E-4_25</t>
+          <t>TEMA 1E-4</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ESTADO 1E_1, 2 o 3</t>
+          <t>ESTADO 1E</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>REVISADO_X_ESTUDIANTE 1E_0 o 1</t>
+          <t>REVISADO_X_ESTUDIANTE 1E</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>FINAL_100</t>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>EXAMEN 2E_100</t>
+          <t>EXAMEN 2E</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>TEMA 2E-1_30</t>
+          <t>TEMA 2E-1</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>TEMA 2E-2_35</t>
+          <t>TEMA 2E-2</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>TEMA 2E-3_35</t>
+          <t>TEMA 2E-3</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ESTADO 2E_1, 2 o 3</t>
+          <t>ESTADO 2E</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>REVISADO_X_ESTUDIANTE 2E_0 o 1</t>
+          <t>REVISADO_X_ESTUDIANTE 2E</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO_100</t>
+          <t>MEJORAMIENTO</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>EXAMEN 3E_100</t>
+          <t>EXAMEN 3E</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>TEMA 3E-1_20</t>
+          <t>TEMA 3E-1</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>TEMA 3E-2_30</t>
+          <t>TEMA 3E-2</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>TEMA 3E-3_50</t>
+          <t>TEMA 3E-3</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>ESTADO 3E_1, 2 o 3</t>
+          <t>ESTADO 3E</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>REVISADO_X_ESTUDIANTE 3E_0 o 1</t>
+          <t>REVISADO_X_ESTUDIANTE 3E</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>PRACTICO_100</t>
+          <t>PRACTICO</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>TALLERES_80</t>
+          <t>TALLERES</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>PARTICIPACION_20</t>
+          <t>PARTICIPACION</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>TRABAJOS_EXTRA_0 o 1</t>
+          <t>TRABAJOS_EXTRA</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>ESTADO_AP, RP o PF</t>
+          <t>ESTADO</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>199645853</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unnamed: 0_level_1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Marta Méndez</t>
+          <t>Unnamed: 1_level_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LI-006</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
+          <t>Unnamed: 2_level_1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1, 2 o 3</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1, 2 o 3</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0 o 1</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" t="n">
+        <v>30</v>
+      </c>
+      <c r="P2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>35</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1, 2 o 3</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0 o 1</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V2" t="n">
+        <v>20</v>
+      </c>
+      <c r="W2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X2" t="n">
         <v>50</v>
       </c>
-      <c r="G2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>63</v>
-      </c>
-      <c r="N2" t="n">
-        <v>56</v>
-      </c>
-      <c r="O2" t="n">
-        <v>12</v>
-      </c>
-      <c r="P2" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>31</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>1, 2 o 3</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0 o 1</t>
+        </is>
       </c>
       <c r="AA2" t="n">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="AB2" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="AC2" t="n">
         <v>20</v>
       </c>
-      <c r="AD2" t="n">
-        <v>1</v>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0 o 1</t>
+        </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP, RP o PF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>199924375</v>
+        <v>199645853</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rosa Wright</t>
+          <t>Marta Méndez</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CI-009</t>
+          <t>LI-006</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
         <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -716,19 +734,19 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="N3" t="n">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="O3" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -758,16 +776,16 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="AB3" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="AC3" t="n">
         <v>20</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -777,38 +795,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>199955764</v>
+        <v>199924375</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Miguel Castillo</t>
+          <t>Rosa Wright</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CI-001</t>
+          <t>CI-009</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -817,19 +835,19 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="O4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -838,25 +856,25 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>74</v>
@@ -878,38 +896,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>199503408</v>
+        <v>199955764</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lucas Paredes</t>
+          <t>Miguel Castillo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LI-005</t>
+          <t>CI-001</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -918,19 +936,19 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N5" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="O5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P5" t="n">
         <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -939,19 +957,19 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="U5" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="V5" t="n">
+        <v>14</v>
+      </c>
+      <c r="W5" t="n">
         <v>8</v>
       </c>
-      <c r="W5" t="n">
-        <v>23</v>
-      </c>
       <c r="X5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
@@ -960,18 +978,119 @@
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="AB5" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="AC5" t="n">
         <v>20</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>199503408</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lucas Paredes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LI-005</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>34</v>
+      </c>
+      <c r="F6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>61</v>
+      </c>
+      <c r="N6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O6" t="n">
+        <v>19</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>26</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>59</v>
+      </c>
+      <c r="U6" t="n">
+        <v>59</v>
+      </c>
+      <c r="V6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>23</v>
+      </c>
+      <c r="X6" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>63</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
